--- a/diseases/d195/2026-2029.xlsx
+++ b/diseases/d195/2026-2029.xlsx
@@ -838,6 +838,296 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>D195</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>pneumoconiosis</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pneumoconiosis</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>D195</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pneumoconiosis</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>尘肺病</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>22</v>
+      </c>
+      <c r="O3" t="n">
+        <v>22</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.01030142597512473</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D195</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pneumoconiosis</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pneumoconiosis</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>D195</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pneumoconiosis</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>尘肺病</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.003277726446630596</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -871,7 +1161,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -954,7 +1244,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -964,7 +1254,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1016,7 +1306,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d195/2026-2029.xlsx
+++ b/diseases/d195/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -909,6 +914,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1045,6 +1055,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1181,6 +1196,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1317,6 +1337,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1453,6 +1478,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1589,6 +1619,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1725,6 +1760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1861,6 +1901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1997,6 +2042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2133,6 +2183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2269,6 +2324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2405,6 +2465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2541,6 +2606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2677,6 +2747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2813,6 +2888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2949,6 +3029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3085,6 +3170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3221,6 +3311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3357,6 +3452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3493,6 +3593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3629,6 +3734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3765,6 +3875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3901,6 +4016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4037,6 +4157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4173,6 +4298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4309,6 +4439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4445,6 +4580,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4581,6 +4721,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4717,6 +4862,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4853,6 +5003,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4989,6 +5144,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5125,6 +5285,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5261,6 +5426,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5397,6 +5567,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5533,6 +5708,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5669,6 +5849,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5805,6 +5990,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5941,6 +6131,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6077,6 +6272,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6213,6 +6413,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6349,6 +6554,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6485,6 +6695,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6621,6 +6836,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6757,6 +6977,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6893,6 +7118,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7029,6 +7259,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7165,6 +7400,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7301,6 +7541,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7437,6 +7682,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7573,6 +7823,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7709,6 +7964,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7845,6 +8105,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7981,6 +8246,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8117,6 +8387,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8253,6 +8528,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8389,6 +8669,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8525,6 +8810,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8661,6 +8951,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8797,6 +9092,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8933,6 +9233,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9069,6 +9374,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9205,6 +9515,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9341,6 +9656,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9477,6 +9797,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9613,6 +9938,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9749,6 +10079,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9885,6 +10220,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10021,6 +10361,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10157,6 +10502,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10293,6 +10643,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10429,6 +10784,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10565,6 +10925,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10701,6 +11066,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10837,6 +11207,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10973,6 +11348,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11109,6 +11489,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11245,6 +11630,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11381,6 +11771,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11517,6 +11912,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11653,6 +12053,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11789,6 +12194,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11925,6 +12335,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12061,6 +12476,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12197,6 +12617,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12333,6 +12758,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12469,6 +12899,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12605,6 +13040,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12741,6 +13181,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12877,6 +13322,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13013,6 +13463,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13149,6 +13604,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13285,6 +13745,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13421,6 +13886,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13557,6 +14027,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13693,6 +14168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13829,6 +14309,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13965,6 +14450,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14101,6 +14591,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14237,6 +14732,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14373,6 +14873,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14509,6 +15014,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14645,6 +15155,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14781,6 +15296,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14917,6 +15437,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15053,6 +15578,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15189,6 +15719,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15325,6 +15860,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15461,6 +16001,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15606,6 +16151,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15742,6 +16292,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15878,6 +16433,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16014,6 +16574,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16150,6 +16715,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16286,6 +16856,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16422,6 +16997,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16558,6 +17138,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16694,6 +17279,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16830,6 +17420,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16966,6 +17561,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17102,6 +17702,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17238,6 +17843,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17374,6 +17984,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17510,6 +18125,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17646,6 +18266,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17782,6 +18407,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17918,6 +18548,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18054,6 +18689,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18190,6 +18830,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18326,6 +18971,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18462,6 +19112,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18598,6 +19253,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18734,6 +19394,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18870,6 +19535,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19006,6 +19676,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19142,6 +19817,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19278,6 +19958,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19414,6 +20099,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19550,6 +20240,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19686,6 +20381,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19822,6 +20522,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19958,6 +20663,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20094,6 +20804,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20230,6 +20945,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20366,6 +21086,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20502,6 +21227,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20638,6 +21368,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20774,6 +21509,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20910,6 +21650,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21046,6 +21791,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21182,6 +21932,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21318,6 +22073,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21454,6 +22214,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21590,6 +22355,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21726,6 +22496,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21862,6 +22637,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21998,6 +22778,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22134,6 +22919,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22270,6 +23060,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22406,6 +23201,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22542,6 +23342,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22678,6 +23483,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22814,6 +23624,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22950,6 +23765,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23095,6 +23915,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23231,6 +24056,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23367,6 +24197,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23503,6 +24338,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23639,6 +24479,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23775,6 +24620,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23911,6 +24761,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24047,6 +24902,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24183,6 +25043,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24319,6 +25184,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24455,6 +25325,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24591,6 +25466,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24727,6 +25607,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24863,6 +25748,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24999,6 +25889,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25135,6 +26030,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25271,6 +26171,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25407,6 +26312,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25543,6 +26453,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25679,6 +26594,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25815,6 +26735,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25951,6 +26876,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26087,6 +27017,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26223,6 +27158,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26359,6 +27299,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26495,6 +27440,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26631,6 +27581,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26767,6 +27722,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26912,6 +27872,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27048,6 +28013,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27184,6 +28154,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27320,6 +28295,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27456,6 +28436,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27592,6 +28577,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27728,6 +28718,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27864,6 +28859,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28000,6 +29000,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28136,6 +29141,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28272,6 +29282,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28408,6 +29423,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28544,6 +29564,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28680,6 +29705,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28816,6 +29846,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28952,6 +29987,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29088,6 +30128,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29224,6 +30269,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29360,6 +30410,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29496,6 +30551,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29632,6 +30692,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29768,6 +30833,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29904,6 +30974,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30040,6 +31115,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30176,6 +31256,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30312,6 +31397,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30446,6 +31536,11 @@
       <c r="S220" t="inlineStr">
         <is>
           <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">

--- a/diseases/d195/2026-2029.xlsx
+++ b/diseases/d195/2026-2029.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,22 +780,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -909,11 +894,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -926,22 +906,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1050,11 +1020,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1067,22 +1032,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1191,11 +1146,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1208,22 +1158,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1332,11 +1272,6 @@
       <c r="R6" t="n">
         <v>0.006716154877755235</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1349,22 +1284,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1473,11 +1398,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1490,22 +1410,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1614,11 +1524,6 @@
       <c r="R8" t="n">
         <v>0.03322263551180799</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1631,22 +1536,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1755,11 +1650,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1772,22 +1662,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1896,11 +1776,6 @@
       <c r="R10" t="n">
         <v>0.01334216940739287</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1913,22 +1788,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2037,11 +1902,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2054,22 +1914,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2178,11 +2028,6 @@
       <c r="R12" t="n">
         <v>0.04659764716364083</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2195,22 +2040,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2319,11 +2154,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2336,22 +2166,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2460,11 +2280,6 @@
       <c r="R14" t="n">
         <v>0.02531434082722203</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2477,22 +2292,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2601,11 +2406,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2618,22 +2418,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2742,11 +2532,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2759,22 +2544,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2883,11 +2658,6 @@
       <c r="R17" t="n">
         <v>0.1043495392341746</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2900,22 +2670,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3024,11 +2784,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3041,22 +2796,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3165,11 +2910,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3182,22 +2922,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3306,11 +3036,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3323,22 +3048,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3447,11 +3162,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3464,22 +3174,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3588,11 +3288,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3605,22 +3300,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3729,11 +3414,6 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3746,22 +3426,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3870,11 +3540,6 @@
       <c r="R24" t="n">
         <v>0.06231463066518999</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3887,22 +3552,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4011,11 +3666,6 @@
       <c r="R25" t="n">
         <v>0.01202970036783215</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4028,22 +3678,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4152,11 +3792,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4169,22 +3804,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4293,11 +3918,6 @@
       <c r="R27" t="n">
         <v>0.002165486101390484</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4310,22 +3930,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4434,11 +4044,6 @@
       <c r="R28" t="n">
         <v>0.1253137543123596</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4451,22 +4056,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4575,11 +4170,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4592,22 +4182,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4716,11 +4296,6 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4733,22 +4308,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4857,11 +4422,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4874,22 +4434,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -4998,11 +4548,6 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5015,22 +4560,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5139,11 +4674,6 @@
       <c r="R33" t="n">
         <v>0.03358077438877618</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5156,22 +4686,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5280,11 +4800,6 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5297,22 +4812,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5421,11 +4926,6 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5438,22 +4938,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5562,11 +5052,6 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5579,22 +5064,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5703,11 +5178,6 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5720,22 +5190,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5844,11 +5304,6 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5861,22 +5316,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -5985,11 +5430,6 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6002,22 +5442,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6126,11 +5556,6 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6143,22 +5568,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6267,11 +5682,6 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6284,22 +5694,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6408,11 +5808,6 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6425,22 +5820,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6549,11 +5934,6 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6566,22 +5946,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6690,11 +6060,6 @@
       <c r="R44" t="n">
         <v>0.01043495392341746</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6707,22 +6072,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6831,11 +6186,6 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6848,22 +6198,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6972,11 +6312,6 @@
       <c r="R46" t="n">
         <v>0.008366481332372193</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6989,22 +6324,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7113,11 +6438,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7130,22 +6450,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7254,11 +6564,6 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7271,22 +6576,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7395,11 +6690,6 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7412,22 +6702,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7536,11 +6816,6 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7553,22 +6828,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7677,11 +6942,6 @@
       <c r="R51" t="n">
         <v>0.0445104504751357</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7694,22 +6954,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7818,11 +7068,6 @@
       <c r="R52" t="n">
         <v>0.01202970036783215</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7835,22 +7080,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -7959,11 +7194,6 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7976,22 +7206,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8100,11 +7320,6 @@
       <c r="R54" t="n">
         <v>0.004330972202780969</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8117,22 +7332,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8241,11 +7446,6 @@
       <c r="R55" t="n">
         <v>0.06265687715617979</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8258,22 +7458,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8382,11 +7572,6 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8399,22 +7584,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8523,11 +7698,6 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8540,22 +7710,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8664,11 +7824,6 @@
       <c r="R58" t="n">
         <v>0.04586181925581861</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8681,22 +7836,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -8805,11 +7950,6 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8822,22 +7962,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8946,11 +8076,6 @@
       <c r="R60" t="n">
         <v>0.006716154877755235</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8963,22 +8088,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9087,11 +8202,6 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9104,22 +8214,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9228,11 +8328,6 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9245,22 +8340,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9369,11 +8454,6 @@
       <c r="R63" t="n">
         <v>0.2168313139110298</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9386,22 +8466,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9510,11 +8580,6 @@
       <c r="R64" t="n">
         <v>0.02668433881478574</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9527,22 +8592,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -9651,11 +8706,6 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9668,22 +8718,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -9792,11 +8832,6 @@
       <c r="R66" t="n">
         <v>0.03261835301454857</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9809,22 +8844,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -9933,11 +8958,6 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9950,22 +8970,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10074,11 +9084,6 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10091,22 +9096,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10215,11 +9210,6 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10232,22 +9222,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10356,11 +9336,6 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10373,22 +9348,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10497,11 +9462,6 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10514,22 +9474,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10638,11 +9588,6 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10655,22 +9600,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -10779,11 +9714,6 @@
       <c r="R73" t="n">
         <v>0.01673296266474439</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10796,22 +9726,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -10920,11 +9840,6 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10937,22 +9852,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11061,11 +9966,6 @@
       <c r="R75" t="n">
         <v>0.05774110447762056</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11078,22 +9978,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11202,11 +10092,6 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11219,22 +10104,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11343,11 +10218,6 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11360,22 +10230,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11484,11 +10344,6 @@
       <c r="R78" t="n">
         <v>0.0445104504751357</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11501,22 +10356,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11625,11 +10470,6 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11642,22 +10482,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -11766,11 +10596,6 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11783,22 +10608,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -11907,11 +10722,6 @@
       <c r="R81" t="n">
         <v>0.01948937491251436</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11924,22 +10734,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12048,11 +10848,6 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12065,22 +10860,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12189,11 +10974,6 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12206,22 +10986,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12330,11 +11100,6 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12347,22 +11112,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12471,11 +11226,6 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12488,22 +11238,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -12612,11 +11352,6 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12629,22 +11364,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -12753,11 +11478,6 @@
       <c r="R87" t="n">
         <v>0.01343230975551047</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12770,22 +11490,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -12894,11 +11604,6 @@
       <c r="R88" t="n">
         <v>0.01075013241475602</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12911,22 +11616,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13035,11 +11730,6 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13052,22 +11742,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13176,11 +11856,6 @@
       <c r="R90" t="n">
         <v>0.2891084185480397</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13193,22 +11868,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13317,11 +11982,6 @@
       <c r="R91" t="n">
         <v>0.01334216940739287</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13334,22 +11994,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13458,11 +12108,6 @@
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13475,22 +12120,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13599,11 +12234,6 @@
       <c r="R93" t="n">
         <v>0.02795858829818449</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13616,22 +12246,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -13740,11 +12360,6 @@
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13757,22 +12372,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -13881,11 +12486,6 @@
       <c r="R95" t="n">
         <v>0.02531434082722203</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13898,22 +12498,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14022,11 +12612,6 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14039,22 +12624,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -14163,11 +12738,6 @@
       <c r="R97" t="n">
         <v>0.02390727039218443</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14180,22 +12750,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -14304,11 +12864,6 @@
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14321,22 +12876,12 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -14445,11 +12990,6 @@
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14462,22 +13002,12 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -14586,11 +13116,6 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14603,22 +13128,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -14727,11 +13242,6 @@
       <c r="R101" t="n">
         <v>0.00580537705633712</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14744,22 +13254,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -14868,11 +13368,6 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14885,22 +13380,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -15009,11 +13494,6 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15026,22 +13506,12 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -15150,11 +13620,6 @@
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15167,22 +13632,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -15291,11 +13746,6 @@
       <c r="R105" t="n">
         <v>0.00890209009502714</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15308,22 +13758,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -15432,11 +13872,6 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15449,22 +13884,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -15573,11 +13998,6 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15590,22 +14010,12 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -15714,11 +14124,6 @@
       <c r="R108" t="n">
         <v>0.004330972202780969</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15731,22 +14136,12 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -15855,11 +14250,6 @@
       <c r="R109" t="n">
         <v>0.06265687715617979</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15872,22 +14262,12 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -15996,11 +14376,6 @@
       <c r="R110" t="n">
         <v>0.01493847558486594</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16013,22 +14388,12 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -16146,11 +14511,6 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16163,22 +14523,12 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -16287,11 +14637,6 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16304,22 +14649,12 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -16428,11 +14763,6 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16445,22 +14775,12 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -16569,11 +14889,6 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16586,22 +14901,12 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -16710,11 +15015,6 @@
       <c r="R115" t="n">
         <v>0.04701308414428665</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16727,22 +15027,12 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -16851,11 +15141,6 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16868,22 +15153,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -16992,11 +15267,6 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17009,22 +15279,12 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -17133,11 +15393,6 @@
       <c r="R118" t="n">
         <v>0.337293154972713</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17150,22 +15405,12 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -17274,11 +15519,6 @@
       <c r="R119" t="n">
         <v>0</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17291,22 +15531,12 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -17415,11 +15645,6 @@
       <c r="R120" t="n">
         <v>0</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17432,22 +15657,12 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -17556,11 +15771,6 @@
       <c r="R121" t="n">
         <v>0.02795858829818449</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17573,22 +15783,12 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -17697,11 +15897,6 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17714,22 +15909,12 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -17838,11 +16023,6 @@
       <c r="R123" t="n">
         <v>0.02531434082722203</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17855,22 +16035,12 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -17979,11 +16149,6 @@
       <c r="R124" t="n">
         <v>0.02284063495137914</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17996,22 +16161,12 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -18120,11 +16275,6 @@
       <c r="R125" t="n">
         <v>0.02390727039218443</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18137,22 +16287,12 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -18261,11 +16401,6 @@
       <c r="R126" t="n">
         <v>0.01043495392341746</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18278,22 +16413,12 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -18402,11 +16527,6 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18419,22 +16539,12 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -18543,11 +16653,6 @@
       <c r="R128" t="n">
         <v>0.02509944399711657</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18560,22 +16665,12 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -18684,11 +16779,6 @@
       <c r="R129" t="n">
         <v>0</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18701,22 +16791,12 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -18825,11 +16905,6 @@
       <c r="R130" t="n">
         <v>0.05774110447762056</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18842,22 +16917,12 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -18966,11 +17031,6 @@
       <c r="R131" t="n">
         <v>0</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18983,22 +17043,12 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -19107,11 +17157,6 @@
       <c r="R132" t="n">
         <v>0</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19124,22 +17169,12 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -19248,11 +17283,6 @@
       <c r="R133" t="n">
         <v>0.01780418019005428</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19265,22 +17295,12 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -19389,11 +17409,6 @@
       <c r="R134" t="n">
         <v>0</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19406,22 +17421,12 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -19530,11 +17535,6 @@
       <c r="R135" t="n">
         <v>0</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19547,22 +17547,12 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -19671,11 +17661,6 @@
       <c r="R136" t="n">
         <v>0.01732388881112388</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19688,22 +17673,12 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -19812,11 +17787,6 @@
       <c r="R137" t="n">
         <v>0</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19829,22 +17799,12 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -19953,11 +17913,6 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19970,22 +17925,12 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -20094,11 +18039,6 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20111,22 +18051,12 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -20235,11 +18165,6 @@
       <c r="R140" t="n">
         <v>0</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20252,22 +18177,12 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -20376,11 +18291,6 @@
       <c r="R141" t="n">
         <v>0</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20393,22 +18303,12 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -20517,11 +18417,6 @@
       <c r="R142" t="n">
         <v>0.02014846463326571</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20534,22 +18429,12 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -20658,11 +18543,6 @@
       <c r="R143" t="n">
         <v>0.02150026482951204</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20675,22 +18555,12 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -20799,11 +18669,6 @@
       <c r="R144" t="n">
         <v>0</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20816,22 +18681,12 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -20940,11 +18795,6 @@
       <c r="R145" t="n">
         <v>0.2891084185480397</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20957,22 +18807,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -21081,11 +18921,6 @@
       <c r="R146" t="n">
         <v>0.01334216940739287</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21098,22 +18933,12 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -21222,11 +19047,6 @@
       <c r="R147" t="n">
         <v>0</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21239,22 +19059,12 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -21363,11 +19173,6 @@
       <c r="R148" t="n">
         <v>0.02329882358182041</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21380,22 +19185,12 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -21504,11 +19299,6 @@
       <c r="R149" t="n">
         <v>0</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21521,22 +19311,12 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -21645,11 +19425,6 @@
       <c r="R150" t="n">
         <v>0</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21662,22 +19437,12 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -21786,11 +19551,6 @@
       <c r="R151" t="n">
         <v>0</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21803,22 +19563,12 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -21927,11 +19677,6 @@
       <c r="R152" t="n">
         <v>0.04781454078436885</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21944,22 +19689,12 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -22068,11 +19803,6 @@
       <c r="R153" t="n">
         <v>0.01043495392341746</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22085,22 +19815,12 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -22209,11 +19929,6 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22226,22 +19941,12 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -22350,11 +20055,6 @@
       <c r="R155" t="n">
         <v>0.01673296266474439</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22367,22 +20067,12 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -22491,11 +20181,6 @@
       <c r="R156" t="n">
         <v>0</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22508,22 +20193,12 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -22632,11 +20307,6 @@
       <c r="R157" t="n">
         <v>0.05774110447762056</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22649,22 +20319,12 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -22773,11 +20433,6 @@
       <c r="R158" t="n">
         <v>0</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22790,22 +20445,12 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -22914,11 +20559,6 @@
       <c r="R159" t="n">
         <v>0</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22931,22 +20571,12 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -23055,11 +20685,6 @@
       <c r="R160" t="n">
         <v>0.03560836038010856</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23072,22 +20697,12 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -23196,11 +20811,6 @@
       <c r="R161" t="n">
         <v>0.02405940073566429</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23213,22 +20823,12 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -23337,11 +20937,6 @@
       <c r="R162" t="n">
         <v>0.04334154655640577</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23354,22 +20949,12 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -23478,11 +21063,6 @@
       <c r="R163" t="n">
         <v>0.002165486101390484</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23495,22 +21075,12 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -23619,11 +21189,6 @@
       <c r="R164" t="n">
         <v>0</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23636,22 +21201,12 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -23760,11 +21315,6 @@
       <c r="R165" t="n">
         <v>0.01027020196459534</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23777,22 +21327,12 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -23910,11 +21450,6 @@
       <c r="R166" t="n">
         <v>0</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23927,22 +21462,12 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -24051,11 +21576,6 @@
       <c r="R167" t="n">
         <v>0</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24068,22 +21588,12 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -24192,11 +21702,6 @@
       <c r="R168" t="n">
         <v>0</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24209,22 +21714,12 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -24333,11 +21828,6 @@
       <c r="R169" t="n">
         <v>0</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24350,22 +21840,12 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -24474,11 +21954,6 @@
       <c r="R170" t="n">
         <v>0.01343230975551047</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24491,22 +21966,12 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -24615,11 +22080,6 @@
       <c r="R171" t="n">
         <v>0.01075013241475602</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24632,22 +22092,12 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -24756,11 +22206,6 @@
       <c r="R172" t="n">
         <v>0</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24773,22 +22218,12 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -24897,11 +22332,6 @@
       <c r="R173" t="n">
         <v>0</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24914,22 +22344,12 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -25038,11 +22458,6 @@
       <c r="R174" t="n">
         <v>0</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25055,22 +22470,12 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -25179,11 +22584,6 @@
       <c r="R175" t="n">
         <v>0</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25196,22 +22596,12 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
         <v>0</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -25320,11 +22710,6 @@
       <c r="R176" t="n">
         <v>0.02329882358182041</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25337,22 +22722,12 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -25461,11 +22836,6 @@
       <c r="R177" t="n">
         <v>0</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25478,22 +22848,12 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -25602,11 +22962,6 @@
       <c r="R178" t="n">
         <v>0</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25619,22 +22974,12 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -25743,11 +23088,6 @@
       <c r="R179" t="n">
         <v>0</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25760,22 +23100,12 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
@@ -25884,11 +23214,6 @@
       <c r="R180" t="n">
         <v>0</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25901,22 +23226,12 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -26025,11 +23340,6 @@
       <c r="R181" t="n">
         <v>0</v>
       </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26042,22 +23352,12 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
         <v>0</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
@@ -26166,11 +23466,6 @@
       <c r="R182" t="n">
         <v>0</v>
       </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26183,22 +23478,12 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
         <v>0</v>
-      </c>
-      <c r="AU182" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
@@ -26307,11 +23592,6 @@
       <c r="R183" t="n">
         <v>0.01673296266474439</v>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26324,22 +23604,12 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
         <v>0</v>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
@@ -26448,11 +23718,6 @@
       <c r="R184" t="n">
         <v>0</v>
       </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26465,22 +23730,12 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
         <v>0</v>
-      </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
@@ -26589,11 +23844,6 @@
       <c r="R185" t="n">
         <v>0</v>
       </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26606,22 +23856,12 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
         <v>0</v>
-      </c>
-      <c r="AU185" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
@@ -26730,11 +23970,6 @@
       <c r="R186" t="n">
         <v>0</v>
       </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26747,22 +23982,12 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
-      </c>
-      <c r="AU186" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -26871,11 +24096,6 @@
       <c r="R187" t="n">
         <v>0</v>
       </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26888,22 +24108,12 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
         <v>0</v>
-      </c>
-      <c r="AU187" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
@@ -27012,11 +24222,6 @@
       <c r="R188" t="n">
         <v>0.03560836038010856</v>
       </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27029,22 +24234,12 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
-      </c>
-      <c r="AU188" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
@@ -27153,11 +24348,6 @@
       <c r="R189" t="n">
         <v>0.01202970036783215</v>
       </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27170,22 +24360,12 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
         <v>0</v>
-      </c>
-      <c r="AU189" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
@@ -27294,11 +24474,6 @@
       <c r="R190" t="n">
         <v>0</v>
       </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27311,22 +24486,12 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
         <v>0</v>
-      </c>
-      <c r="AU190" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
@@ -27435,11 +24600,6 @@
       <c r="R191" t="n">
         <v>0.01299291660834291</v>
       </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27452,22 +24612,12 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
         <v>0</v>
-      </c>
-      <c r="AU191" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
@@ -27576,11 +24726,6 @@
       <c r="R192" t="n">
         <v>0.06265687715617979</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27593,22 +24738,12 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
-      </c>
-      <c r="AU192" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -27717,11 +24852,6 @@
       <c r="R193" t="n">
         <v>0.003267791534189425</v>
       </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27734,22 +24864,12 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
-      </c>
-      <c r="AU193" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -27867,11 +24987,6 @@
       <c r="R194" t="n">
         <v>0</v>
       </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27884,22 +24999,12 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
         <v>0</v>
-      </c>
-      <c r="AU194" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
@@ -28008,11 +25113,6 @@
       <c r="R195" t="n">
         <v>0</v>
       </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28025,22 +25125,12 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
         <v>0</v>
-      </c>
-      <c r="AU195" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
@@ -28149,11 +25239,6 @@
       <c r="R196" t="n">
         <v>0</v>
       </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28166,22 +25251,12 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
         <v>0</v>
-      </c>
-      <c r="AU196" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
@@ -28290,11 +25365,6 @@
       <c r="R197" t="n">
         <v>0</v>
       </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28307,22 +25377,12 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
         <v>0</v>
-      </c>
-      <c r="AU197" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
@@ -28431,11 +25491,6 @@
       <c r="R198" t="n">
         <v>0</v>
       </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28448,22 +25503,12 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
         <v>0</v>
-      </c>
-      <c r="AU198" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
@@ -28572,11 +25617,6 @@
       <c r="R199" t="n">
         <v>0</v>
       </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28589,22 +25629,12 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
         <v>0</v>
-      </c>
-      <c r="AU199" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
@@ -28713,11 +25743,6 @@
       <c r="R200" t="n">
         <v>0</v>
       </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28730,22 +25755,12 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
         <v>0</v>
-      </c>
-      <c r="AU200" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
@@ -28854,11 +25869,6 @@
       <c r="R201" t="n">
         <v>0.04818473642467328</v>
       </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28871,22 +25881,12 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
         <v>0</v>
-      </c>
-      <c r="AU201" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
@@ -28995,11 +25995,6 @@
       <c r="R202" t="n">
         <v>0</v>
       </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29012,22 +26007,12 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
         <v>0</v>
-      </c>
-      <c r="AU202" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
@@ -29136,11 +26121,6 @@
       <c r="R203" t="n">
         <v>0</v>
       </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29153,22 +26133,12 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
         <v>0</v>
-      </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
@@ -29277,11 +26247,6 @@
       <c r="R204" t="n">
         <v>0.009319529432728164</v>
       </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29294,22 +26259,12 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
         <v>0</v>
-      </c>
-      <c r="AU204" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
@@ -29418,11 +26373,6 @@
       <c r="R205" t="n">
         <v>0</v>
       </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29435,22 +26385,12 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
         <v>0</v>
-      </c>
-      <c r="AU205" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
@@ -29559,11 +26499,6 @@
       <c r="R206" t="n">
         <v>0</v>
       </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29576,22 +26511,12 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
         <v>0</v>
-      </c>
-      <c r="AU206" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
@@ -29700,11 +26625,6 @@
       <c r="R207" t="n">
         <v>0</v>
       </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29717,22 +26637,12 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
         <v>0</v>
-      </c>
-      <c r="AU207" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
@@ -29841,11 +26751,6 @@
       <c r="R208" t="n">
         <v>0</v>
       </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29858,22 +26763,12 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
         <v>0</v>
-      </c>
-      <c r="AU208" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
@@ -29982,11 +26877,6 @@
       <c r="R209" t="n">
         <v>0</v>
       </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29999,22 +26889,12 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
         <v>0</v>
-      </c>
-      <c r="AU209" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
@@ -30123,11 +27003,6 @@
       <c r="R210" t="n">
         <v>0</v>
       </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30140,22 +27015,12 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
         <v>0</v>
-      </c>
-      <c r="AU210" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
@@ -30264,11 +27129,6 @@
       <c r="R211" t="n">
         <v>0.008366481332372193</v>
       </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30281,22 +27141,12 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
         <v>0</v>
-      </c>
-      <c r="AU211" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
@@ -30405,11 +27255,6 @@
       <c r="R212" t="n">
         <v>0</v>
       </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30422,22 +27267,12 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
         <v>0</v>
-      </c>
-      <c r="AU212" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
@@ -30546,11 +27381,6 @@
       <c r="R213" t="n">
         <v>0</v>
       </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30563,22 +27393,12 @@
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr"/>
       <c r="AT213" t="n">
         <v>0</v>
-      </c>
-      <c r="AU213" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
@@ -30687,11 +27507,6 @@
       <c r="R214" t="n">
         <v>0</v>
       </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30704,22 +27519,12 @@
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr"/>
       <c r="AT214" t="n">
         <v>0</v>
-      </c>
-      <c r="AU214" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
@@ -30828,11 +27633,6 @@
       <c r="R215" t="n">
         <v>0</v>
       </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30845,22 +27645,12 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
         <v>0</v>
-      </c>
-      <c r="AU215" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
@@ -30969,11 +27759,6 @@
       <c r="R216" t="n">
         <v>0.00890209009502714</v>
       </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30986,22 +27771,12 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
         <v>0</v>
-      </c>
-      <c r="AU216" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
@@ -31110,11 +27885,6 @@
       <c r="R217" t="n">
         <v>0.01202970036783215</v>
       </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31127,22 +27897,12 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr"/>
       <c r="AT217" t="n">
         <v>0</v>
-      </c>
-      <c r="AU217" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
@@ -31251,11 +28011,6 @@
       <c r="R218" t="n">
         <v>0</v>
       </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31268,22 +28023,12 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
         <v>0</v>
-      </c>
-      <c r="AU218" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
@@ -31392,11 +28137,6 @@
       <c r="R219" t="n">
         <v>0</v>
       </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31409,22 +28149,12 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr"/>
       <c r="AT219" t="n">
         <v>0</v>
-      </c>
-      <c r="AU219" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
@@ -31533,11 +28263,6 @@
       <c r="R220" t="n">
         <v>0</v>
       </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31550,22 +28275,12 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
         <v>0</v>
-      </c>
-      <c r="AU220" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
